--- a/Result/profitability/3413.xlsx
+++ b/Result/profitability/3413.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM62"/>
+  <dimension ref="A1:AM63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.02</v>
       </c>
       <c r="M2" t="n">
-        <v>4.73875</v>
+        <v>4.625</v>
       </c>
       <c r="N2" t="n">
-        <v>24.05</v>
+        <v>23.49125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-3.56</v>
       </c>
       <c r="M3" t="n">
-        <v>3.60375</v>
+        <v>3.2275</v>
       </c>
       <c r="N3" t="n">
-        <v>20.1875</v>
+        <v>19.775</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-3.06</v>
       </c>
       <c r="M4" t="n">
-        <v>2.26875</v>
+        <v>2.00625</v>
       </c>
       <c r="N4" t="n">
-        <v>14.3525</v>
+        <v>13.72375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-2.94</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0625</v>
+        <v>1.2125</v>
       </c>
       <c r="N5" t="n">
-        <v>11.13625</v>
+        <v>10.65875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.16</v>
       </c>
       <c r="M6" t="n">
-        <v>0.65625</v>
+        <v>0.4700000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>10.17375</v>
+        <v>10.0175</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.07</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02750000000000002</v>
+        <v>-0.05749999999999994</v>
       </c>
       <c r="N7" t="n">
-        <v>9.203749999999999</v>
+        <v>9.001249999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -8302,6 +8302,133 @@
       </c>
       <c r="AM62" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>3413</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>6300</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4896</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1404</v>
+      </c>
+      <c r="F63" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="G63" t="n">
+        <v>769</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>12.21%</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>-76</v>
+      </c>
+      <c r="J63" t="n">
+        <v>693</v>
+      </c>
+      <c r="K63" t="n">
+        <v>511</v>
+      </c>
+      <c r="L63" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="M63" t="n">
+        <v>5.4425</v>
+      </c>
+      <c r="N63" t="n">
+        <v>24.91125</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
+      </c>
+      <c r="V63" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0.3300000000000001</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0.07710280373831768</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>-1.559999999999999</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-0.06543624161073824</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0.3519061583577714</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>-3.82</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>-0.146360153256705</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK63" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
